--- a/files/STable-1.xlsx
+++ b/files/STable-1.xlsx
@@ -11,6 +11,251 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+  <si>
+    <t>Accesion</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>1081</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>1061</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,793 +599,633 @@
   <dimension ref="A1:B79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Accesion</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1040</t>
-        </is>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1025</t>
-        </is>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1094</t>
-        </is>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>24</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>25</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>26</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>27</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>28</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>29</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>30</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>32</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>33</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>34</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1089</t>
-        </is>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>35</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>36</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>37</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>38</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>39</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>40</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>41</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>42</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>43</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>44</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>45</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>46</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>47</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>48</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>49</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>50</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>51</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>52</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>53</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>54</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>55</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>56</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>57</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>58</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>59</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>60</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>61</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>62</v>
       </c>
       <c r="B62">
         <v>3</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>63</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>64</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>65</v>
       </c>
       <c r="B65">
         <v>4</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1077</t>
-        </is>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>66</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>67</v>
       </c>
       <c r="B67">
         <v>5</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>68</v>
       </c>
       <c r="B68">
         <v>5</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>69</v>
       </c>
       <c r="B69">
         <v>5</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>70</v>
       </c>
       <c r="B70">
         <v>5</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>71</v>
       </c>
       <c r="B71">
         <v>5</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>72</v>
       </c>
       <c r="B72">
         <v>5</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>73</v>
       </c>
       <c r="B73">
         <v>5</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>74</v>
       </c>
       <c r="B74">
         <v>5</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>75</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>76</v>
       </c>
       <c r="B76">
         <v>4</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>77</v>
       </c>
       <c r="B77">
         <v>5</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>78</v>
       </c>
       <c r="B78">
         <v>5</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>79</v>
       </c>
       <c r="B79">
         <v>5</v>
